--- a/data/trans_camb/IP1013-Clase-trans_camb.xlsx
+++ b/data/trans_camb/IP1013-Clase-trans_camb.xlsx
@@ -631,32 +631,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,2; 2,97</t>
+          <t>-1,2; 2,44</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-3,26; 0,0</t>
+          <t>-3,02; 0,0</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-2,79; 0,0</t>
+          <t>-3,77; 0,0</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-3,05; 0,0</t>
+          <t>-3,82; 0,0</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-1,31; 1,08</t>
+          <t>-1,32; 0,81</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-2,28; 0,0</t>
+          <t>-2,51; 0,0</t>
         </is>
       </c>
     </row>
@@ -1099,17 +1099,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,56; 1,74</t>
+          <t>-0,63; 1,78</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-1,75; 0,0</t>
+          <t>-1,6; 0,0</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,77</t>
+          <t>0,0; 1,97</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -1119,12 +1119,12 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-0,02; 1,28</t>
+          <t>-0,16; 1,29</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-0,86; 0,0</t>
+          <t>-1,05; 0,0</t>
         </is>
       </c>
     </row>
@@ -1260,12 +1260,12 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0,42; 4,33</t>
+          <t>0,43; 3,98</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,46</t>
+          <t>0,0; 3,19</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
@@ -1275,12 +1275,12 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,2</t>
+          <t>0,0; 1,43</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,21; 2,05</t>
+          <t>0,21; 2,31</t>
         </is>
       </c>
     </row>
@@ -1567,17 +1567,17 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-0,29; 0,61</t>
+          <t>-0,29; 0,72</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-0,3; 0,59</t>
+          <t>-0,3; 0,58</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-0,12; 0,56</t>
+          <t>-0,13; 0,64</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
@@ -1587,12 +1587,12 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-0,1; 0,49</t>
+          <t>-0,11; 0,46</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-0,24; 0,26</t>
+          <t>-0,24; 0,24</t>
         </is>
       </c>
     </row>
@@ -1663,7 +1663,7 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-66,15; —</t>
+          <t>-78,76; —</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">

--- a/data/trans_camb/IP1013-Clase-trans_camb.xlsx
+++ b/data/trans_camb/IP1013-Clase-trans_camb.xlsx
@@ -631,32 +631,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,2; 2,44</t>
+          <t>-1,2; 2,43</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-3,02; 0,0</t>
+          <t>-2,76; 0,0</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-3,77; 0,0</t>
+          <t>-4,05; 0,0</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-3,82; 0,0</t>
+          <t>-4,63; 0,0</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-1,32; 0,81</t>
+          <t>-1,31; 0,85</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-2,51; 0,0</t>
+          <t>-2,21; 0,0</t>
         </is>
       </c>
     </row>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,63; 1,78</t>
+          <t>-0,62; 1,72</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -1109,7 +1109,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,97</t>
+          <t>0,0; 1,75</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -1119,12 +1119,12 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-0,16; 1,29</t>
+          <t>-0,15; 1,27</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-1,05; 0,0</t>
+          <t>-0,64; 0,0</t>
         </is>
       </c>
     </row>
@@ -1260,12 +1260,12 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0,43; 3,98</t>
+          <t>0,44; 4,61</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,19</t>
+          <t>0,0; 2,49</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
@@ -1275,12 +1275,12 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,43</t>
+          <t>0,0; 1,19</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,21; 2,31</t>
+          <t>0,0; 1,93</t>
         </is>
       </c>
     </row>
@@ -1567,17 +1567,17 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-0,29; 0,72</t>
+          <t>-0,29; 0,63</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-0,3; 0,58</t>
+          <t>-0,3; 0,63</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-0,13; 0,64</t>
+          <t>-0,11; 0,56</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
@@ -1587,12 +1587,12 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-0,11; 0,46</t>
+          <t>-0,1; 0,45</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-0,24; 0,24</t>
+          <t>-0,25; 0,25</t>
         </is>
       </c>
     </row>
@@ -1663,7 +1663,7 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-78,76; —</t>
+          <t>-74,63; 989,65</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">

--- a/data/trans_camb/IP1013-Clase-trans_camb.xlsx
+++ b/data/trans_camb/IP1013-Clase-trans_camb.xlsx
@@ -519,13 +519,13 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="F1" s="3" t="n"/>
@@ -593,22 +593,22 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>-0,69</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>-0,69</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
           <t>0,15</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>-0,6</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>-0,69</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>-0,69</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -631,32 +631,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,2; 2,43</t>
+          <t>-2,79; 0,0</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-2,76; 0,0</t>
+          <t>-3,05; 0,0</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-4,05; 0,0</t>
+          <t>-1,2; 2,97</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-4,63; 0,0</t>
+          <t>-3,26; 0,0</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-1,31; 0,85</t>
+          <t>-1,31; 1,08</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-2,21; 0,0</t>
+          <t>-2,28; 0,0</t>
         </is>
       </c>
     </row>
@@ -669,17 +669,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>-100,0%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>-100,0%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
           <t>25,3%</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -1061,22 +1061,22 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>0,57</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
           <t>0,37</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="F16" s="2" t="inlineStr">
         <is>
           <t>-0,32</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>0,57</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,62; 1,72</t>
+          <t>0,0; 1,77</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-1,6; 0,0</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,75</t>
+          <t>-0,56; 1,74</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-1,75; 0,0</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-0,15; 1,27</t>
+          <t>-0,02; 1,28</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-0,64; 0,0</t>
+          <t>-0,86; 0,0</t>
         </is>
       </c>
     </row>
@@ -1137,22 +1137,22 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>inf%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
           <t>115,3%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="F18" s="2" t="inlineStr">
         <is>
           <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1217,22 +1217,22 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>0,49</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
           <t>1,52</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>0,49</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1255,32 +1255,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 2,46</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0,44; 4,61</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,49</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,42; 4,33</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,19</t>
+          <t>0,0; 1,2</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,93</t>
+          <t>0,21; 2,05</t>
         </is>
       </c>
     </row>
@@ -1293,22 +1293,22 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>inf%</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
           <t>inf%</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -1529,22 +1529,22 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>0,18</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>-0,1</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
           <t>0,11</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="F28" s="2" t="inlineStr">
         <is>
           <t>0,11</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>0,18</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>-0,1</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -1567,32 +1567,32 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-0,29; 0,63</t>
+          <t>-0,12; 0,56</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-0,3; 0,63</t>
+          <t>-0,49; 0,0</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-0,11; 0,56</t>
+          <t>-0,29; 0,61</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-0,49; 0,0</t>
+          <t>-0,3; 0,59</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-0,1; 0,45</t>
+          <t>-0,1; 0,49</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-0,25; 0,25</t>
+          <t>-0,24; 0,26</t>
         </is>
       </c>
     </row>
@@ -1605,22 +1605,22 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
+          <t>182,08%</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>-100,0%</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
           <t>55,68%</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="F30" s="2" t="inlineStr">
         <is>
           <t>56,07%</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>182,08%</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -1663,7 +1663,7 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-74,63; 989,65</t>
+          <t>-66,15; —</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
